--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>273</v>
+        <v>221</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>148</v>
+        <v>312</v>
       </c>
       <c r="D3">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>39</v>
-      </c>
-      <c r="G3">
-        <v>115</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>312</v>
       </c>
       <c r="D3">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H3">
         <v>426</v>
